--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>10:54:14 AM</v>
+        <v>10:58:59 AM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>10:54:15 AM</v>
+        <v>10:58:59 AM</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>10:54:15 AM</v>
+        <v>10:59:00 AM</v>
       </c>
       <c r="H4">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>10:54:15 AM</v>
+        <v>10:59:00 AM</v>
       </c>
       <c r="H5">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,7 +575,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>10:54:15 AM</v>
+        <v>10:59:00 AM</v>
       </c>
       <c r="H6">
         <v>279</v>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H9">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H10">
         <v>15</v>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H11">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>10:54:16 AM</v>
+        <v>10:59:01 AM</v>
       </c>
       <c r="H12">
         <v>19</v>
@@ -778,10 +778,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>10:54:17 AM</v>
+        <v>10:59:02 AM</v>
       </c>
       <c r="H13">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -807,10 +807,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>10:54:17 AM</v>
+        <v>10:59:02 AM</v>
       </c>
       <c r="H14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>10:54:17 AM</v>
+        <v>10:59:02 AM</v>
       </c>
       <c r="H15">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>10:54:18 AM</v>
+        <v>10:59:03 AM</v>
       </c>
       <c r="H16">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>10:54:18 AM</v>
+        <v>10:59:03 AM</v>
       </c>
       <c r="H17">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>10:54:18 AM</v>
+        <v>10:59:03 AM</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>10:54:18 AM</v>
+        <v>10:59:03 AM</v>
       </c>
       <c r="H19">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>10:54:18 AM</v>
+        <v>10:59:03 AM</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,10 +1010,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H21">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H24">
         <v>14</v>
@@ -1130,10 +1130,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>10:54:19 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H26">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,10 +1188,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="str">
         <v>Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) HeadlessChrome/149.0.0.0 Safari/537.36</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H28">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:04 AM</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1275,7 +1275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H30">
         <v>302</v>
@@ -1304,7 +1304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H31">
         <v>11</v>
@@ -1333,10 +1333,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1362,10 +1362,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H35">
         <v>14</v>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H37">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 399ms</v>
+        <v>Time to interact: 354ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,10 +1509,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H38">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I38" t="str">
         <v>Status: 200</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H39">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,10 +1567,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="str">
         <v>Value: 0</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,7 +1625,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H42">
         <v>3</v>
@@ -1654,10 +1654,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" t="str">
         <v>Value: false</v>
@@ -1683,7 +1683,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -1741,10 +1741,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="str">
         <v>Value: true</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -1887,7 +1887,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -1916,10 +1916,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1945,7 +1945,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H53">
         <v>3</v>
@@ -1974,7 +1974,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -2003,10 +2003,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2032,7 +2032,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -2090,10 +2090,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" t="str">
         <v>Array Length: 1</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>10:54:20 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,10 +2148,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2177,7 +2177,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H61">
         <v>6</v>
@@ -2206,10 +2206,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2235,10 +2235,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2264,7 +2264,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H67">
         <v>15</v>
@@ -2380,10 +2380,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H68">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I68" t="str">
         <v>Count: 3</v>
@@ -2409,10 +2409,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2438,10 +2438,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2467,10 +2467,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2496,7 +2496,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -2525,10 +2525,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2554,7 +2554,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:05 AM</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -2583,7 +2583,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,10 +2641,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H77">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I77" t="str">
         <v>Lang: en</v>
@@ -2670,7 +2670,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H78">
         <v>8</v>
@@ -2699,10 +2699,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2728,7 +2728,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -2757,7 +2757,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2786,7 +2786,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -2815,10 +2815,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2844,10 +2844,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2873,7 +2873,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H85">
         <v>2</v>
@@ -2902,7 +2902,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H86">
         <v>3</v>
@@ -2931,10 +2931,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H87">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I87" t="str">
         <v>Width: 1280px</v>
@@ -2960,7 +2960,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H88">
         <v>14</v>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,7 +3018,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H90">
         <v>4</v>
@@ -3047,10 +3047,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H93">
         <v>3</v>
@@ -3134,10 +3134,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3163,7 +3163,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3192,7 +3192,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H96">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,10 +3251,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" t="str">
         <v>GEO-PROOF DASHBOARD</v>
@@ -3280,10 +3280,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3309,7 +3309,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H100">
         <v>3</v>
@@ -3338,10 +3338,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3367,7 +3367,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H102">
         <v>3</v>
@@ -3396,10 +3396,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -3425,7 +3425,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H104">
         <v>3</v>
@@ -3454,10 +3454,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -3483,10 +3483,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>10:54:21 AM</v>
+        <v>10:59:06 AM</v>
       </c>
       <c r="H106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>10:54:22 AM</v>
+        <v>10:59:07 AM</v>
       </c>
       <c r="H107">
-        <v>1037</v>
+        <v>1010</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>10:54:23 AM</v>
+        <v>10:59:08 AM</v>
       </c>
       <c r="H108">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>10:54:24 AM</v>
+        <v>10:59:09 AM</v>
       </c>
       <c r="H109">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>10:54:24 AM</v>
+        <v>10:59:09 AM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>10:54:25 AM</v>
+        <v>10:59:09 AM</v>
       </c>
       <c r="H111">
         <v>0</v>

--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>10:58:59 AM</v>
+        <v>11:00:22 AM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>10:58:59 AM</v>
+        <v>11:00:22 AM</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>10:59:00 AM</v>
+        <v>11:00:23 AM</v>
       </c>
       <c r="H4">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>10:59:00 AM</v>
+        <v>11:00:23 AM</v>
       </c>
       <c r="H5">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>10:59:00 AM</v>
+        <v>11:00:23 AM</v>
       </c>
       <c r="H6">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H7">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H8">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H9">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,10 +691,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H11">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>10:59:01 AM</v>
+        <v>11:00:24 AM</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12" t="str">
         <v>Camera permission blocked or hardware busy. Please upload an image directly under the 'Upload' tab.</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>10:59:02 AM</v>
+        <v>11:00:25 AM</v>
       </c>
       <c r="H13">
         <v>559</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>10:59:02 AM</v>
+        <v>11:00:25 AM</v>
       </c>
       <c r="H14">
         <v>15</v>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>10:59:02 AM</v>
+        <v>11:00:25 AM</v>
       </c>
       <c r="H15">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>10:59:03 AM</v>
+        <v>11:00:26 AM</v>
       </c>
       <c r="H16">
         <v>367</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>10:59:03 AM</v>
+        <v>11:00:26 AM</v>
       </c>
       <c r="H17">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,7 +923,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>10:59:03 AM</v>
+        <v>11:00:26 AM</v>
       </c>
       <c r="H18">
         <v>15</v>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>10:59:03 AM</v>
+        <v>11:00:26 AM</v>
       </c>
       <c r="H19">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>10:59:03 AM</v>
+        <v>11:00:26 AM</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,10 +1010,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H21">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H24">
         <v>14</v>
@@ -1130,10 +1130,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:27 AM</v>
       </c>
       <c r="H26">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,10 +1188,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
         <v>Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) HeadlessChrome/149.0.0.0 Safari/537.36</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H28">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>10:59:04 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1275,7 +1275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H30">
         <v>302</v>
@@ -1304,10 +1304,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H33">
         <v>13</v>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,10 +1421,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H37">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 354ms</v>
+        <v>Time to interact: 413ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,7 +1509,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H38">
         <v>16</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H39">
-        <v>304</v>
+        <v>373</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,10 +1567,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" t="str">
         <v>Value: 0</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H41">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,10 +1625,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" t="str">
         <v>Value: true</v>
@@ -1654,7 +1654,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H43">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -1712,10 +1712,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" t="str">
         <v>Value: true</v>
@@ -1741,10 +1741,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="str">
         <v>Value: true</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:28 AM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -1887,10 +1887,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1916,7 +1916,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -1945,10 +1945,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -2032,7 +2032,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -2090,7 +2090,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,10 +2148,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2177,10 +2177,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2206,7 +2206,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -2235,10 +2235,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2264,10 +2264,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H67">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I67" t="str">
         <v>Before: 2, After: 3</v>
@@ -2380,10 +2380,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I68" t="str">
         <v>Count: 3</v>
@@ -2409,7 +2409,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2438,7 +2438,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2496,7 +2496,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -2525,7 +2525,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H73">
         <v>3</v>
@@ -2554,7 +2554,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>10:59:05 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -2583,10 +2583,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,7 +2641,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H77">
         <v>13</v>
@@ -2670,7 +2670,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H78">
         <v>8</v>
@@ -2699,7 +2699,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H79">
         <v>3</v>
@@ -2728,7 +2728,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -2757,7 +2757,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2786,7 +2786,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -2815,7 +2815,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -2844,10 +2844,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2873,10 +2873,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2902,10 +2902,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2931,7 +2931,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H87">
         <v>206</v>
@@ -2960,10 +2960,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H88">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,10 +3018,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3047,7 +3047,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3076,10 +3076,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3105,10 +3105,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3134,10 +3134,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3163,7 +3163,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3192,7 +3192,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:29 AM</v>
       </c>
       <c r="H96">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H98">
         <v>13</v>
@@ -3280,7 +3280,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -3309,7 +3309,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H100">
         <v>3</v>
@@ -3338,10 +3338,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3367,7 +3367,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H102">
         <v>3</v>
@@ -3396,7 +3396,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -3425,7 +3425,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H104">
         <v>3</v>
@@ -3454,10 +3454,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -3483,7 +3483,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>10:59:06 AM</v>
+        <v>11:00:30 AM</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>10:59:07 AM</v>
+        <v>11:00:31 AM</v>
       </c>
       <c r="H107">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>10:59:08 AM</v>
+        <v>11:00:31 AM</v>
       </c>
       <c r="H108">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>10:59:09 AM</v>
+        <v>11:00:32 AM</v>
       </c>
       <c r="H109">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>10:59:09 AM</v>
+        <v>11:00:32 AM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>10:59:09 AM</v>
+        <v>11:00:33 AM</v>
       </c>
       <c r="H111">
         <v>0</v>

--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:00:22 AM</v>
+        <v>11:01:31 AM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:00:22 AM</v>
+        <v>11:01:32 AM</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:00:23 AM</v>
+        <v>11:01:32 AM</v>
       </c>
       <c r="H4">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:00:23 AM</v>
+        <v>11:01:32 AM</v>
       </c>
       <c r="H5">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:00:23 AM</v>
+        <v>11:01:32 AM</v>
       </c>
       <c r="H6">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H8">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H9">
-        <v>268</v>
+        <v>317</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,10 +691,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H10">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H11">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:00:24 AM</v>
+        <v>11:01:33 AM</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" t="str">
         <v>Camera permission blocked or hardware busy. Please upload an image directly under the 'Upload' tab.</v>
@@ -778,10 +778,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:00:25 AM</v>
+        <v>11:01:34 AM</v>
       </c>
       <c r="H13">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -807,10 +807,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:00:25 AM</v>
+        <v>11:01:34 AM</v>
       </c>
       <c r="H14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:00:25 AM</v>
+        <v>11:01:34 AM</v>
       </c>
       <c r="H15">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:00:26 AM</v>
+        <v>11:01:35 AM</v>
       </c>
       <c r="H16">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:00:26 AM</v>
+        <v>11:01:35 AM</v>
       </c>
       <c r="H17">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:00:26 AM</v>
+        <v>11:01:35 AM</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:00:26 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H19">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:00:26 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,10 +1010,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H21">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H24">
         <v>14</v>
@@ -1130,10 +1130,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:00:27 AM</v>
+        <v>11:01:36 AM</v>
       </c>
       <c r="H26">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,10 +1188,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="str">
         <v>Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) HeadlessChrome/149.0.0.0 Safari/537.36</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H28">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1275,10 +1275,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H30">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1304,10 +1304,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1362,10 +1362,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,10 +1421,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H37">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 413ms</v>
+        <v>Time to interact: 398ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,10 +1509,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I38" t="str">
         <v>Status: 200</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H39">
-        <v>373</v>
+        <v>12</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,10 +1567,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="str">
         <v>Value: 0</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H41">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,10 +1625,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="str">
         <v>Value: true</v>
@@ -1654,10 +1654,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
         <v>Value: false</v>
@@ -1683,10 +1683,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
         <v>Value: true</v>
@@ -1712,7 +1712,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H46">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:00:28 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1887,7 +1887,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -1916,10 +1916,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1945,10 +1945,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1974,7 +1974,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H54">
         <v>6</v>
@@ -2003,7 +2003,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -2032,10 +2032,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2061,10 +2061,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2090,7 +2090,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -2177,7 +2177,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -2206,7 +2206,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -2235,7 +2235,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -2264,10 +2264,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H67">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I67" t="str">
         <v>Before: 2, After: 3</v>
@@ -2380,10 +2380,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H68">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I68" t="str">
         <v>Count: 3</v>
@@ -2409,7 +2409,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2438,10 +2438,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2467,10 +2467,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2496,10 +2496,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2525,10 +2525,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2554,10 +2554,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2583,10 +2583,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,10 +2641,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H77">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I77" t="str">
         <v>Lang: en</v>
@@ -2670,10 +2670,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H78">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I78" t="str">
         <v>H1 count: 0</v>
@@ -2699,10 +2699,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2728,10 +2728,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2786,10 +2786,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2815,7 +2815,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:37 AM</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -2873,7 +2873,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H85">
         <v>3</v>
@@ -2902,10 +2902,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2931,10 +2931,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H87">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I87" t="str">
         <v>Width: 1280px</v>
@@ -2960,10 +2960,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H88">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,7 +3018,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3047,7 +3047,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3076,10 +3076,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3105,10 +3105,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3134,7 +3134,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H94">
         <v>3</v>
@@ -3163,10 +3163,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3192,10 +3192,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:00:29 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,10 +3251,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" t="str">
         <v>GEO-PROOF DASHBOARD</v>
@@ -3280,10 +3280,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H99">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3309,10 +3309,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -3338,10 +3338,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3367,7 +3367,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H102">
         <v>3</v>
@@ -3396,10 +3396,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -3425,7 +3425,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H104">
         <v>3</v>
@@ -3454,10 +3454,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -3483,10 +3483,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:00:30 AM</v>
+        <v>11:01:38 AM</v>
       </c>
       <c r="H106">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>11:00:31 AM</v>
+        <v>11:01:39 AM</v>
       </c>
       <c r="H107">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>11:00:31 AM</v>
+        <v>11:01:40 AM</v>
       </c>
       <c r="H108">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>11:00:32 AM</v>
+        <v>11:01:41 AM</v>
       </c>
       <c r="H109">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>11:00:32 AM</v>
+        <v>11:01:41 AM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>11:00:33 AM</v>
+        <v>11:01:42 AM</v>
       </c>
       <c r="H111">
         <v>0</v>

--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:01:31 AM</v>
+        <v>11:02:36 AM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:01:32 AM</v>
+        <v>11:02:36 AM</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:01:32 AM</v>
+        <v>11:02:36 AM</v>
       </c>
       <c r="H4">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:01:32 AM</v>
+        <v>11:02:36 AM</v>
       </c>
       <c r="H5">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:01:32 AM</v>
+        <v>11:02:37 AM</v>
       </c>
       <c r="H6">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:37 AM</v>
       </c>
       <c r="H7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:37 AM</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:37 AM</v>
       </c>
       <c r="H9">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,10 +691,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:37 AM</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:38 AM</v>
       </c>
       <c r="H11">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:01:33 AM</v>
+        <v>11:02:38 AM</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I12" t="str">
         <v>Camera permission blocked or hardware busy. Please upload an image directly under the 'Upload' tab.</v>
@@ -778,10 +778,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:01:34 AM</v>
+        <v>11:02:38 AM</v>
       </c>
       <c r="H13">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -807,10 +807,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:01:34 AM</v>
+        <v>11:02:38 AM</v>
       </c>
       <c r="H14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:01:34 AM</v>
+        <v>11:02:38 AM</v>
       </c>
       <c r="H15">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:01:35 AM</v>
+        <v>11:02:39 AM</v>
       </c>
       <c r="H16">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:01:35 AM</v>
+        <v>11:02:39 AM</v>
       </c>
       <c r="H17">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:01:35 AM</v>
+        <v>11:02:39 AM</v>
       </c>
       <c r="H18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H19">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,10 +1010,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H21">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H24">
         <v>14</v>
@@ -1130,10 +1130,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:01:36 AM</v>
+        <v>11:02:40 AM</v>
       </c>
       <c r="H26">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,10 +1188,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
         <v>Mozilla/5.0 (X11; Linux x86_64) AppleWebKit/537.36 (KHTML, like Gecko) HeadlessChrome/149.0.0.0 Safari/537.36</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H28">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1275,10 +1275,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H30">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1304,10 +1304,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H32">
         <v>11</v>
@@ -1362,10 +1362,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H33">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,10 +1421,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H37">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 398ms</v>
+        <v>Time to interact: 380ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,10 +1509,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:41 AM</v>
       </c>
       <c r="H38">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I38" t="str">
         <v>Status: 200</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H39">
-        <v>12</v>
+        <v>495</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,7 +1567,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,7 +1625,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H42">
         <v>3</v>
@@ -1654,10 +1654,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" t="str">
         <v>Value: false</v>
@@ -1683,10 +1683,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" t="str">
         <v>Value: true</v>
@@ -1712,7 +1712,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1741,10 +1741,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="str">
         <v>Value: true</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H50">
         <v>4</v>
@@ -1887,7 +1887,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -1916,10 +1916,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1945,10 +1945,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1974,7 +1974,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H54">
         <v>6</v>
@@ -2003,10 +2003,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2032,10 +2032,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2061,10 +2061,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2090,10 +2090,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I58" t="str">
         <v>Array Length: 1</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -2177,10 +2177,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2206,7 +2206,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -2235,7 +2235,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -2264,10 +2264,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H67">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I67" t="str">
         <v>Before: 2, After: 3</v>
@@ -2380,10 +2380,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H68">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I68" t="str">
         <v>Count: 3</v>
@@ -2409,7 +2409,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2438,10 +2438,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2467,10 +2467,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2496,10 +2496,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2525,10 +2525,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2554,10 +2554,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2583,7 +2583,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,10 +2641,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H77">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I77" t="str">
         <v>Lang: en</v>
@@ -2670,10 +2670,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H78">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I78" t="str">
         <v>H1 count: 0</v>
@@ -2699,10 +2699,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2728,10 +2728,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2786,10 +2786,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2815,7 +2815,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:01:37 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -2873,10 +2873,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2902,10 +2902,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2931,10 +2931,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H87">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I87" t="str">
         <v>Width: 1280px</v>
@@ -2960,10 +2960,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H88">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,10 +3018,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3047,7 +3047,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3076,7 +3076,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H92">
         <v>3</v>
@@ -3105,10 +3105,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3134,7 +3134,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H94">
         <v>3</v>
@@ -3163,10 +3163,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3192,10 +3192,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:42 AM</v>
       </c>
       <c r="H96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,10 +3251,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" t="str">
         <v>GEO-PROOF DASHBOARD</v>
@@ -3280,10 +3280,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3309,10 +3309,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -3338,7 +3338,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H101">
         <v>3</v>
@@ -3367,10 +3367,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -3396,7 +3396,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H103">
         <v>3</v>
@@ -3425,10 +3425,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -3454,7 +3454,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H105">
         <v>3</v>
@@ -3483,10 +3483,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:01:38 AM</v>
+        <v>11:02:43 AM</v>
       </c>
       <c r="H106">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>11:01:39 AM</v>
+        <v>11:02:44 AM</v>
       </c>
       <c r="H107">
-        <v>1032</v>
+        <v>995</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>11:01:40 AM</v>
+        <v>11:02:45 AM</v>
       </c>
       <c r="H108">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>11:01:41 AM</v>
+        <v>11:02:45 AM</v>
       </c>
       <c r="H109">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>11:01:41 AM</v>
+        <v>11:02:46 AM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>11:01:42 AM</v>
+        <v>11:02:46 AM</v>
       </c>
       <c r="H111">
         <v>0</v>

--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:02:36 AM</v>
+        <v>11:02:57 AM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:02:36 AM</v>
+        <v>11:02:58 AM</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:02:36 AM</v>
+        <v>11:02:58 AM</v>
       </c>
       <c r="H4">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:02:36 AM</v>
+        <v>11:02:58 AM</v>
       </c>
       <c r="H5">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:02:37 AM</v>
+        <v>11:02:58 AM</v>
       </c>
       <c r="H6">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:02:37 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H7">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:02:37 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:02:37 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H9">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:02:37 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H10">
         <v>15</v>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:02:38 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H11">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:02:38 AM</v>
+        <v>11:02:59 AM</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I12" t="str">
         <v>Camera permission blocked or hardware busy. Please upload an image directly under the 'Upload' tab.</v>
@@ -778,10 +778,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:02:38 AM</v>
+        <v>11:03:00 AM</v>
       </c>
       <c r="H13">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -807,10 +807,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:02:38 AM</v>
+        <v>11:03:00 AM</v>
       </c>
       <c r="H14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:02:38 AM</v>
+        <v>11:03:00 AM</v>
       </c>
       <c r="H15">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:02:39 AM</v>
+        <v>11:03:01 AM</v>
       </c>
       <c r="H16">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:02:39 AM</v>
+        <v>11:03:01 AM</v>
       </c>
       <c r="H17">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:02:39 AM</v>
+        <v>11:03:01 AM</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H19">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,10 +1010,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H21">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1039,10 +1039,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,10 +1098,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" t="str" xml:space="preserve">
         <v xml:space="preserve">© 2026 MUKESH G / SIMATS ENGINEERING
@@ -1130,7 +1130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:02:40 AM</v>
+        <v>11:03:02 AM</v>
       </c>
       <c r="H26">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,7 +1188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H27">
         <v>4</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H28">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1275,7 +1275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H30">
         <v>302</v>
@@ -1304,7 +1304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -1333,10 +1333,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H32">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H33">
         <v>13</v>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H35">
         <v>13</v>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H37">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 380ms</v>
+        <v>Time to interact: 363ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,10 +1509,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:02:41 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" t="str">
         <v>Status: 200</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H39">
-        <v>495</v>
+        <v>6</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,10 +1567,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" t="str">
         <v>Value: 0</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H41">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,7 +1625,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H42">
         <v>3</v>
@@ -1654,7 +1654,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H43">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H46">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1887,7 +1887,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -1916,7 +1916,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -1945,10 +1945,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2003,10 +2003,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2032,7 +2032,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -2090,10 +2090,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" t="str">
         <v>Array Length: 1</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,10 +2148,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2177,10 +2177,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2206,7 +2206,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -2235,7 +2235,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -2264,7 +2264,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H64">
         <v>4</v>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H67">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I67" t="str">
         <v>Before: 2, After: 3</v>
@@ -2380,7 +2380,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H68">
         <v>12</v>
@@ -2409,7 +2409,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2438,7 +2438,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2467,7 +2467,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -2496,7 +2496,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -2525,10 +2525,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2554,7 +2554,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H74">
         <v>4</v>
@@ -2583,7 +2583,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,7 +2641,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H77">
         <v>13</v>
@@ -2670,10 +2670,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I78" t="str">
         <v>H1 count: 0</v>
@@ -2699,10 +2699,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2728,7 +2728,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -2757,10 +2757,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2786,7 +2786,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -2815,7 +2815,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -2844,10 +2844,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2873,10 +2873,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2902,10 +2902,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:03 AM</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2931,10 +2931,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H87">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I87" t="str">
         <v>Width: 1280px</v>
@@ -2960,10 +2960,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H88">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,10 +3018,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3047,7 +3047,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3076,7 +3076,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H92">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H94">
         <v>3</v>
@@ -3163,7 +3163,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3192,7 +3192,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:02:42 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H96">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,10 +3251,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H98">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I98" t="str">
         <v>GEO-PROOF DASHBOARD</v>
@@ -3280,7 +3280,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -3309,10 +3309,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -3338,10 +3338,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -3396,10 +3396,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -3425,10 +3425,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -3454,7 +3454,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H105">
         <v>3</v>
@@ -3483,7 +3483,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:02:43 AM</v>
+        <v>11:03:04 AM</v>
       </c>
       <c r="H106">
         <v>2</v>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>11:02:44 AM</v>
+        <v>11:03:05 AM</v>
       </c>
       <c r="H107">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>11:02:45 AM</v>
+        <v>11:03:06 AM</v>
       </c>
       <c r="H108">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>11:02:45 AM</v>
+        <v>11:03:07 AM</v>
       </c>
       <c r="H109">
         <v>510</v>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>11:02:46 AM</v>
+        <v>11:03:07 AM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>11:02:46 AM</v>
+        <v>11:03:07 AM</v>
       </c>
       <c r="H111">
         <v>0</v>

--- a/test-analysis-report-categories.xlsx
+++ b/test-analysis-report-categories.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:02:57 AM</v>
+        <v>5:33:14 PM</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:02:58 AM</v>
+        <v>5:33:14 PM</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:02:58 AM</v>
+        <v>5:33:14 PM</v>
       </c>
       <c r="H4">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:02:58 AM</v>
+        <v>5:33:14 PM</v>
       </c>
       <c r="H5">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,7 +575,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:02:58 AM</v>
+        <v>5:33:15 PM</v>
       </c>
       <c r="H6">
         <v>278</v>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:15 PM</v>
       </c>
       <c r="H7">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:15 PM</v>
       </c>
       <c r="H8">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,10 +662,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:15 PM</v>
       </c>
       <c r="H9">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -691,10 +691,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:15 PM</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:16 PM</v>
       </c>
       <c r="H11">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:02:59 AM</v>
+        <v>5:33:16 PM</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" t="str">
         <v>Camera permission blocked or hardware busy. Please upload an image directly under the 'Upload' tab.</v>
@@ -778,10 +778,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:03:00 AM</v>
+        <v>5:33:16 PM</v>
       </c>
       <c r="H13">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:03:00 AM</v>
+        <v>5:33:16 PM</v>
       </c>
       <c r="H14">
         <v>15</v>
@@ -836,10 +836,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:03:00 AM</v>
+        <v>5:33:17 PM</v>
       </c>
       <c r="H15">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:03:01 AM</v>
+        <v>5:33:17 PM</v>
       </c>
       <c r="H16">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:03:01 AM</v>
+        <v>5:33:17 PM</v>
       </c>
       <c r="H17">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:03:01 AM</v>
+        <v>5:33:17 PM</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H19">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H21">
         <v>357</v>
@@ -1039,10 +1039,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1098,10 +1098,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I24" t="str" xml:space="preserve">
         <v xml:space="preserve">© 2026 MUKESH G / SIMATS ENGINEERING
@@ -1130,7 +1130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -1159,10 +1159,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:03:02 AM</v>
+        <v>5:33:18 PM</v>
       </c>
       <c r="H26">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I26" t="str">
         <v>Found 4 cards.</v>
@@ -1188,7 +1188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H27">
         <v>4</v>
@@ -1217,10 +1217,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H28">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1246,10 +1246,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H30">
         <v>302</v>
@@ -1304,7 +1304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -1333,10 +1333,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H33">
         <v>13</v>
@@ -1391,7 +1391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1421,10 +1421,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1450,7 +1450,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1480,13 +1480,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H37">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="I37" t="str">
-        <v>Time to interact: 363ms</v>
+        <v>Time to interact: 352ms</v>
       </c>
     </row>
     <row r="38">
@@ -1509,10 +1509,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:19 PM</v>
       </c>
       <c r="H38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" t="str">
         <v>Status: 200</v>
@@ -1538,10 +1538,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>365</v>
       </c>
       <c r="I39" t="str">
         <v>Status: 200</v>
@@ -1567,10 +1567,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="str">
         <v>Value: 0</v>
@@ -1596,10 +1596,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I41" t="str">
         <v>Value: true</v>
@@ -1625,10 +1625,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I42" t="str">
         <v>Value: true</v>
@@ -1654,7 +1654,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H43">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H46">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -1828,7 +1828,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -1887,7 +1887,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -1916,7 +1916,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -1945,7 +1945,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H53">
         <v>3</v>
@@ -1974,7 +1974,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -2003,7 +2003,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -2032,7 +2032,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -2090,7 +2090,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -2148,10 +2148,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2177,7 +2177,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -2206,7 +2206,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -2235,10 +2235,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2264,7 +2264,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H64">
         <v>4</v>
@@ -2293,7 +2293,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H67">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" t="str">
         <v>Before: 2, After: 3</v>
@@ -2380,7 +2380,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H68">
         <v>12</v>
@@ -2409,7 +2409,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2438,7 +2438,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2496,10 +2496,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2525,7 +2525,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H73">
         <v>3</v>
@@ -2554,10 +2554,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2583,7 +2583,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2612,7 +2612,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2641,10 +2641,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H77">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I77" t="str">
         <v>Lang: en</v>
@@ -2670,10 +2670,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I78" t="str">
         <v>H1 count: 0</v>
@@ -2699,7 +2699,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H79">
         <v>4</v>
@@ -2728,7 +2728,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -2757,10 +2757,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2786,7 +2786,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -2815,7 +2815,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -2844,10 +2844,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2873,10 +2873,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2902,10 +2902,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:03:03 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2931,10 +2931,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H87">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I87" t="str">
         <v>Width: 1280px</v>
@@ -2960,10 +2960,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H88">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3018,7 +3018,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3047,10 +3047,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3076,7 +3076,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H92">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H94">
         <v>3</v>
@@ -3163,7 +3163,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3192,7 +3192,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:20 PM</v>
       </c>
       <c r="H96">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3251,10 +3251,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H98">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I98" t="str">
         <v>GEO-PROOF DASHBOARD</v>
@@ -3280,7 +3280,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -3309,7 +3309,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H100">
         <v>3</v>
@@ -3338,10 +3338,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3367,10 +3367,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -3396,10 +3396,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -3425,10 +3425,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -3454,10 +3454,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -3483,10 +3483,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:03:04 AM</v>
+        <v>5:33:21 PM</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -3512,10 +3512,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G107" t="str">
-        <v>11:03:05 AM</v>
+        <v>5:33:22 PM</v>
       </c>
       <c r="H107">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -3541,10 +3541,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>11:03:06 AM</v>
+        <v>5:33:23 PM</v>
       </c>
       <c r="H108">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G109" t="str">
-        <v>11:03:07 AM</v>
+        <v>5:33:23 PM</v>
       </c>
       <c r="H109">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G110" t="str">
-        <v>11:03:07 AM</v>
+        <v>5:33:24 PM</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G111" t="str">
-        <v>11:03:07 AM</v>
+        <v>5:33:24 PM</v>
       </c>
       <c r="H111">
         <v>0</v>
